--- a/outputs/collections_summary.xlsx
+++ b/outputs/collections_summary.xlsx
@@ -1,16 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30606"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDCED0D6-2722-4BC5-B3FA-0D08E496F3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30610"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30ECBA5C-A979-4980-BE31-6D0D5892CAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="RollMatrix" sheetId="5" r:id="rId2"/>
+    <sheet name="BackTest" sheetId="4" r:id="rId3"/>
+    <sheet name="RollRates" sheetId="2" r:id="rId4"/>
+    <sheet name="BucketSummary" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="231" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,9 +40,143 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
+  <si>
+    <t>Collections Prioritization: Summary</t>
+  </si>
+  <si>
+    <t>Source: Kaggle Home Credit sample (30,000 customers), early-stage collections (1-90 DPD)</t>
+  </si>
+  <si>
+    <t>Roll rates by delinquency bucket</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Next-month transitions</t>
+  </si>
+  <si>
+    <t>Cured to current</t>
+  </si>
+  <si>
+    <t>Cure Rate</t>
+  </si>
+  <si>
+    <t>Account-months (backtest base)</t>
+  </si>
+  <si>
+    <t>Rolled to worse bucket</t>
+  </si>
+  <si>
+    <t>1-30</t>
+  </si>
+  <si>
+    <t>31-60</t>
+  </si>
+  <si>
+    <t>61-90</t>
+  </si>
+  <si>
+    <t>Backtest at 10% contact capacity</t>
+  </si>
+  <si>
+    <t>Oldest-first capture at 10%</t>
+  </si>
+  <si>
+    <t>Alternative (v3) capture at 10%</t>
+  </si>
+  <si>
+    <t>Random picking</t>
+  </si>
+  <si>
+    <t>Lift of oldest-first vs random (x)</t>
+  </si>
+  <si>
+    <t>Gap: v3 minus oldest-first (pp)</t>
+  </si>
+  <si>
+    <t>Key findings</t>
+  </si>
+  <si>
+    <t>Early lateness mostly cures: 45.8% of 1-30 day accounts return to current next month.</t>
+  </si>
+  <si>
+    <t>Risk climbs with lateness: 62.1% of 31-60 and 92.5% of 61-90 day accounts roll into a worse bucket.</t>
+  </si>
+  <si>
+    <t>Oldest-first captures about 6x random at 10% capacity; weighting by loan amount did not beat it.</t>
+  </si>
+  <si>
+    <t>Limitation: public data with no contact log, so this shows targeting quality only.</t>
+  </si>
+  <si>
+    <t>Share of Row</t>
+  </si>
+  <si>
+    <t>Next Month</t>
+  </si>
+  <si>
+    <t>This Month</t>
+  </si>
+  <si>
+    <t>0 Current</t>
+  </si>
+  <si>
+    <t>90+</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>capacity_pct</t>
+  </si>
+  <si>
+    <t>baseline_capture</t>
+  </si>
+  <si>
+    <t>v1_bucket_x_exposure</t>
+  </si>
+  <si>
+    <t>v2_dpdband_x_exposure</t>
+  </si>
+  <si>
+    <t>v3_band_then_exposure</t>
+  </si>
+  <si>
+    <t>random_capture</t>
+  </si>
+  <si>
+    <t>bucket</t>
+  </si>
+  <si>
+    <t>next_bucket</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>account_months</t>
+  </si>
+  <si>
+    <t>pct_bad_next</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -43,16 +184,59 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -60,17 +244,447 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -81,6 +695,1887 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Exposure captured vs contact capacity</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"Oldest first"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Oldest first</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BackTest!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BackTest!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.45700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.59699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.80700000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.89</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5744-4961-8754-B2D75A28C64B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"V1: bucket x amount"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V1: bucket x amount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BackTest!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BackTest!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.57699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.627</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.72399999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5744-4961-8754-B2D75A28C64B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"V2: DPD band x amount"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V2: DPD band x amount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BackTest!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BackTest!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.437</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52200000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.63200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.68899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.79300000000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5744-4961-8754-B2D75A28C64B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"V3: DPD band, then amount"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>V3: DPD band, then amount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BackTest!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BackTest!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.45300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.68500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.79700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.88600000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5744-4961-8754-B2D75A28C64B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>{"Random"}</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Random</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:srgbClr val="808080"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>BackTest!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>BackTest!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5744-4961-8754-B2D75A28C64B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="598918664"/>
+        <c:axId val="598920712"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="598918664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.55000000000000004"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Share of overdue accounts contacted</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="598920712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="598920712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Share of risky exposure captured</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="598918664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44C5E745-CFBE-48B9-97C5-247D1302C4D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46310.529232754627" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="27" xr:uid="{B8E5B93D-2ED5-446B-B2BD-F54778611D93}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tblRoll"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="bucket" numFmtId="0">
+      <sharedItems count="5">
+        <s v="0 Current"/>
+        <s v="1-30"/>
+        <s v="31-60"/>
+        <s v="61-90"/>
+        <s v="90+"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="next_bucket" numFmtId="0">
+      <sharedItems count="6">
+        <s v="0 Current"/>
+        <s v="1-30"/>
+        <s v="31-60"/>
+        <s v="90+"/>
+        <s v="Closed"/>
+        <s v="61-90"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="n" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="714528"/>
+    </cacheField>
+    <cacheField name="pct" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="95.7"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="27">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="714528"/>
+    <n v="91.1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="8796"/>
+    <n v="1.1000000000000001"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="25"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="27"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="60751"/>
+    <n v="7.7"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="6572"/>
+    <n v="45.8"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="5805"/>
+    <n v="40.4"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="641"/>
+    <n v="4.5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="14"/>
+    <n v="0.1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="1325"/>
+    <n v="9.1999999999999993"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="80"/>
+    <n v="11.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="54"/>
+    <n v="7.7"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="42"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="432"/>
+    <n v="61.9"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <n v="9"/>
+    <n v="1.3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <n v="81"/>
+    <n v="11.6"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="11"/>
+    <n v="2.4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="0.4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="0.4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="3"/>
+    <n v="0.7"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="416"/>
+    <n v="91.4"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="21"/>
+    <n v="4.5999999999999996"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="199"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="9306"/>
+    <n v="95.7"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="218"/>
+    <n v="2.2000000000000002"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E95F098-71D5-46DD-ACFB-6C8A44472209}" name="PivotTable1" cacheId="231" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:H9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField name="This Month" axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField name="Next Month" axis="axisCol" compact="0" outline="0" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Share of Row" fld="2" showDataAs="percentOfRow" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <formats count="4">
+    <format dxfId="17">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0" selected="0"/>
+          <reference field="1" count="5" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="0" grandCol="1" outline="0" axis="axisRow" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="20">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="4" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="6" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5C163BF9-59D1-484D-BE90-D7C1727ECEDC}" name="tblGain" displayName="tblGain" ref="A1:F6" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:F6" xr:uid="{5C163BF9-59D1-484D-BE90-D7C1727ECEDC}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{7C4D5AFB-653C-4356-82B7-4C036DD2C2B0}" name="capacity_pct" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{EADFE43F-E653-4607-85D1-064C3EAD162A}" name="baseline_capture" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B2470E7A-E1F1-476E-ADA7-AF70940D9F17}" name="v1_bucket_x_exposure" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{2297EB52-27E9-4F1D-B6BA-CB1310B07191}" name="v2_dpdband_x_exposure" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{DDC20B9A-CA1A-4E9C-A969-925ED3FA25C5}" name="v3_band_then_exposure" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{63EA4C97-65D6-42F0-AE07-1FB9F46E321F}" name="random_capture" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5DD181F2-51C3-4823-929E-D82D9F8C43FC}" name="tblRoll" displayName="tblRoll" ref="A1:D28" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:D28" xr:uid="{5DD181F2-51C3-4823-929E-D82D9F8C43FC}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{DDDBE0AF-BEE0-4CA2-A1F8-1ACAC6E2380F}" name="bucket" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3E679327-ED56-4DDF-9BC7-906C6B34C477}" name="next_bucket" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{7F6D9240-1343-4A29-B690-F4961D8FDE6E}" name="n" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{BFE7953D-16EC-4944-88FE-E5A28B32BC71}" name="pct" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0DDAEF75-A1C4-4055-BCD7-538121426149}" name="tblBucket" displayName="tblBucket" ref="A1:C4" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:C4" xr:uid="{0DDAEF75-A1C4-4055-BCD7-538121426149}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{264E5B8D-42E7-4A19-BB82-D9A6BDA263BC}" name="bucket"/>
+    <tableColumn id="2" xr3:uid="{6AEB1FFC-7ABB-4B9E-BE22-E049A40F533B}" name="account_months" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{33655FA8-EDA7-4E16-8F93-779C4160E77C}" name="pct_bad_next" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -380,9 +2875,1008 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="28.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75">
+      <c r="A3" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A5)</f>
+        <v>14357</v>
+      </c>
+      <c r="C5" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A5, tblRoll[next_bucket], "0 Current")</f>
+        <v>6572</v>
+      </c>
+      <c r="D5" s="3">
+        <f>C5/B5</f>
+        <v>0.45775579856515985</v>
+      </c>
+      <c r="E5" s="15">
+        <f>_xlfn.XLOOKUP($A5, tblBucket[bucket], tblBucket[account_months], "n/a")</f>
+        <v>13607</v>
+      </c>
+      <c r="F5" s="3">
+        <f>_xlfn.XLOOKUP($A5, tblBucket[bucket], tblBucket[pct_bad_next], "n/a")/100</f>
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A6)</f>
+        <v>698</v>
+      </c>
+      <c r="C6" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A6, tblRoll[next_bucket], "0 Current")</f>
+        <v>80</v>
+      </c>
+      <c r="D6" s="3">
+        <f t="shared" ref="D6:D7" si="0">C6/B6</f>
+        <v>0.11461318051575932</v>
+      </c>
+      <c r="E6" s="15">
+        <f>_xlfn.XLOOKUP($A6, tblBucket[bucket], tblBucket[account_months], "n/a")</f>
+        <v>601</v>
+      </c>
+      <c r="F6" s="3">
+        <f>_xlfn.XLOOKUP($A6, tblBucket[bucket], tblBucket[pct_bad_next], "n/a")/100</f>
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A7)</f>
+        <v>455</v>
+      </c>
+      <c r="C7" s="15">
+        <f>SUMIFS(tblRoll[n], tblRoll[bucket], $A7, tblRoll[next_bucket], "0 Current")</f>
+        <v>11</v>
+      </c>
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>2.4175824175824177E-2</v>
+      </c>
+      <c r="E7" s="15">
+        <f>_xlfn.XLOOKUP($A7, tblBucket[bucket], tblBucket[account_months], "n/a")</f>
+        <v>372</v>
+      </c>
+      <c r="F7" s="3">
+        <f>_xlfn.XLOOKUP($A7, tblBucket[bucket], tblBucket[pct_bad_next], "n/a")/100</f>
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75">
+      <c r="A10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="16">
+        <f>_xlfn.XLOOKUP(0.1, tblGain[capacity_pct], tblGain[baseline_capture], "n/a")</f>
+        <v>0.59699999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="17">
+        <f>_xlfn.XLOOKUP(0.1, tblGain[capacity_pct], tblGain[v3_band_then_exposure], "n/a")</f>
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="17">
+        <f>_xlfn.XLOOKUP(0.1, tblGain[capacity_pct], tblGain[random_capture], "n/a")</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="13">
+        <f>B11/B13</f>
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="18">
+        <f>(B12-B11)*100</f>
+        <v>-0.70000000000000062</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86716B50-45C3-48A2-8D17-3AC6B592CEB1}">
+  <dimension ref="A3:H9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.91124014349716309</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.1217570623126101E-2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.1882590447720838E-5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.4433197683538512E-5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7.7475970091579555E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.45775579856515985</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.4043323814167305</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.4647210420004177E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>9.7513408093612868E-4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>9.2289475517169331E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.11461318051575932</v>
+      </c>
+      <c r="C7" s="3">
+        <v>7.7363896848137534E-2</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.0171919770773637E-2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.61891117478510027</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1.2893982808022923E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.11604584527220631</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2.4175824175824177E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4.3956043956043956E-3</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4.3956043956043956E-3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6.5934065934065934E-3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4.6153846153846156E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2.0460621015833846E-2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.0563438206868187E-4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.0281719103434094E-4</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.95681677976557677</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2.2414147645486326E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting pivot="1" sqref="B5:G9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B87D67-796C-40F7-BF72-CD88DB787CA5}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.437</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.627</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEAA688-27DE-48F8-B807-7C24A2513F46}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1">
+        <v>714528</v>
+      </c>
+      <c r="D2" s="1">
+        <v>91.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1">
+        <v>8796</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1">
+        <v>60751</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6572</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5805</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>641</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1325</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1">
+        <v>432</v>
+      </c>
+      <c r="D15" s="1">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1">
+        <v>81</v>
+      </c>
+      <c r="D17" s="1">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1">
+        <v>416</v>
+      </c>
+      <c r="D22" s="1">
+        <v>91.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1">
+        <v>199</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="1">
+        <v>9306</v>
+      </c>
+      <c r="D27" s="1">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="1">
+        <v>218</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BC172EC-BC88-435D-B362-12484597750A}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1">
+        <v>13607</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>601</v>
+      </c>
+      <c r="C3" s="1">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>372</v>
+      </c>
+      <c r="C4" s="1">
+        <v>92.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>